--- a/files_result_11.07.2025/Поставщики комплектующих.xlsx
+++ b/files_result_11.07.2025/Поставщики комплектующих.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65B2F4C-B478-415F-8368-AC055F8907DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07CC4A65-2E59-4D92-BDB2-B11F65CD02A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Аурум Фуд" sheetId="13" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="77">
   <si>
     <t>дата поставки</t>
   </si>
@@ -421,7 +421,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -441,19 +441,6 @@
       </top>
       <bottom style="thin">
         <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -485,12 +472,57 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -554,10 +586,6 @@
     <xf numFmtId="2" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -565,9 +593,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -600,46 +625,95 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="12" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="12" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="10" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1355,7 +1429,7 @@
     <col min="6" max="6" width="8.85546875" style="1"/>
     <col min="7" max="7" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.85546875" style="1"/>
-    <col min="9" max="9" width="15.28515625" style="42" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" style="39" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
@@ -1384,7 +1458,7 @@
       <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="40" t="s">
+      <c r="I1" s="37" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1399,7 +1473,7 @@
       <c r="F2" s="3"/>
       <c r="G2" s="6"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="41">
+      <c r="I2" s="38">
         <v>0</v>
       </c>
     </row>
@@ -1418,7 +1492,7 @@
       <c r="H3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="41">
+      <c r="I3" s="38">
         <f>I2-E3+G3</f>
         <v>265000</v>
       </c>
@@ -1443,7 +1517,7 @@
       <c r="F4" s="3"/>
       <c r="G4" s="6"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="41">
+      <c r="I4" s="38">
         <f t="shared" ref="I4:I21" si="0">I3-E4+G4</f>
         <v>-19928</v>
       </c>
@@ -1459,7 +1533,7 @@
       <c r="F5" s="23"/>
       <c r="G5" s="25"/>
       <c r="H5" s="23"/>
-      <c r="I5" s="46">
+      <c r="I5" s="43">
         <f t="shared" si="0"/>
         <v>-19928</v>
       </c>
@@ -1479,7 +1553,7 @@
       <c r="H6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="41">
+      <c r="I6" s="38">
         <f t="shared" si="0"/>
         <v>245072</v>
       </c>
@@ -1504,7 +1578,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="6"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="41">
+      <c r="I7" s="38">
         <f t="shared" si="0"/>
         <v>212</v>
       </c>
@@ -1527,7 +1601,7 @@
       <c r="H8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="41">
+      <c r="I8" s="38">
         <f t="shared" si="0"/>
         <v>213908</v>
       </c>
@@ -1552,7 +1626,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="6"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="41">
+      <c r="I9" s="38">
         <f t="shared" si="0"/>
         <v>212</v>
       </c>
@@ -1577,7 +1651,7 @@
       <c r="F10" s="3"/>
       <c r="G10" s="6"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="41">
+      <c r="I10" s="38">
         <f t="shared" si="0"/>
         <v>-35404</v>
       </c>
@@ -1602,7 +1676,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="6"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="41">
+      <c r="I11" s="38">
         <f t="shared" si="0"/>
         <v>-71020</v>
       </c>
@@ -1619,7 +1693,7 @@
       <c r="F12" s="3"/>
       <c r="G12" s="6"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="41">
+      <c r="I12" s="38">
         <f t="shared" si="0"/>
         <v>-71020</v>
       </c>
@@ -1636,7 +1710,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="6"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="41">
+      <c r="I13" s="38">
         <f t="shared" si="0"/>
         <v>-71020</v>
       </c>
@@ -1653,7 +1727,7 @@
       <c r="F14" s="3"/>
       <c r="G14" s="6"/>
       <c r="H14" s="3"/>
-      <c r="I14" s="41">
+      <c r="I14" s="38">
         <f t="shared" si="0"/>
         <v>-71020</v>
       </c>
@@ -1670,7 +1744,7 @@
       <c r="F15" s="3"/>
       <c r="G15" s="6"/>
       <c r="H15" s="3"/>
-      <c r="I15" s="41">
+      <c r="I15" s="38">
         <f t="shared" si="0"/>
         <v>-71020</v>
       </c>
@@ -1687,7 +1761,7 @@
       <c r="F16" s="3"/>
       <c r="G16" s="6"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="41">
+      <c r="I16" s="38">
         <f t="shared" si="0"/>
         <v>-71020</v>
       </c>
@@ -1704,7 +1778,7 @@
       <c r="F17" s="3"/>
       <c r="G17" s="6"/>
       <c r="H17" s="3"/>
-      <c r="I17" s="41">
+      <c r="I17" s="38">
         <f t="shared" si="0"/>
         <v>-71020</v>
       </c>
@@ -1721,7 +1795,7 @@
       <c r="F18" s="3"/>
       <c r="G18" s="6"/>
       <c r="H18" s="3"/>
-      <c r="I18" s="41">
+      <c r="I18" s="38">
         <f t="shared" si="0"/>
         <v>-71020</v>
       </c>
@@ -1738,7 +1812,7 @@
       <c r="F19" s="3"/>
       <c r="G19" s="6"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="41">
+      <c r="I19" s="38">
         <f t="shared" si="0"/>
         <v>-71020</v>
       </c>
@@ -1755,7 +1829,7 @@
       <c r="F20" s="3"/>
       <c r="G20" s="6"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="41">
+      <c r="I20" s="38">
         <f t="shared" si="0"/>
         <v>-71020</v>
       </c>
@@ -1772,7 +1846,7 @@
       <c r="F21" s="3"/>
       <c r="G21" s="6"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="41">
+      <c r="I21" s="38">
         <f t="shared" si="0"/>
         <v>-600808</v>
       </c>
@@ -3174,7 +3248,7 @@
       <c r="A22" s="12">
         <v>45709</v>
       </c>
-      <c r="B22" s="50" t="s">
+      <c r="B22" s="47" t="s">
         <v>56</v>
       </c>
       <c r="C22" s="20">
@@ -3199,7 +3273,7 @@
       <c r="A23" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="60" t="s">
+      <c r="B23" s="50" t="s">
         <v>65</v>
       </c>
       <c r="C23" s="8">
@@ -3700,12 +3774,12 @@
     <col min="1" max="1" width="11.140625" style="14" customWidth="1"/>
     <col min="2" max="2" width="18.28515625" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.28515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" style="37"/>
-    <col min="5" max="5" width="14.42578125" style="37" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" style="35"/>
+    <col min="5" max="5" width="14.42578125" style="35" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.85546875" style="14"/>
-    <col min="7" max="7" width="14.42578125" style="37" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="35" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.85546875" style="14"/>
-    <col min="9" max="9" width="15.28515625" style="37" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" style="35" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
@@ -3739,7 +3813,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="44" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="3"/>
@@ -3804,20 +3878,20 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="45" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="23"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F5" s="48"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="36">
+      <c r="C5" s="45"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F5" s="45"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="34">
         <f t="shared" si="1"/>
         <v>-304862</v>
       </c>
@@ -4932,662 +5006,798 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" style="35" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" style="33" customWidth="1"/>
     <col min="3" max="3" width="9.28515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" style="37" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="37" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" style="35" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="35" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.85546875" style="1"/>
     <col min="7" max="7" width="14.85546875" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.85546875" style="1"/>
-    <col min="9" max="9" width="15.28515625" style="37" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" style="35" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="2" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9" t="s">
+      <c r="A1" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="56" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="21">
+      <c r="B2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="60">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="5">
+      <c r="A3" s="61"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="64">
         <v>45559</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="62">
         <v>149976</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="21">
+      <c r="I3" s="60">
         <f>I2-E3+G3</f>
         <v>149976</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+      <c r="A4" s="64">
         <v>45569</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="63">
         <v>6000</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="60">
         <v>24.995999999999999</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="60">
         <f>C4*D4</f>
         <v>149976</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="21">
+      <c r="F4" s="61"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="60">
         <f t="shared" ref="I4:I29" si="0">I3-E4+G4</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="36">
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="68">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="5">
+      <c r="A6" s="61"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="64">
         <v>45677</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="62">
         <v>55152</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="21">
+      <c r="I6" s="60">
         <f t="shared" si="0"/>
         <v>55152</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="14" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="12">
+      <c r="A7" s="70">
         <v>45686</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="63">
         <v>3800</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="60">
         <v>13.788</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="60">
         <f>C7*D7</f>
         <v>52394.400000000001</v>
       </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="21">
+      <c r="F7" s="59"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="60">
         <f t="shared" si="0"/>
         <v>2757.5999999999985</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="32">
+      <c r="A8" s="61"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="71">
         <v>45698</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="62">
         <v>137880</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="60">
         <f t="shared" si="0"/>
         <v>140637.6</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="5">
+      <c r="A9" s="61"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="63"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="64">
         <v>45701</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="72">
         <v>15261.6</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="I9" s="21">
+      <c r="I9" s="60">
         <f t="shared" si="0"/>
         <v>155899.20000000001</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="33">
+      <c r="A10" s="61"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="72">
         <v>44910</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="I10" s="21">
+      <c r="I10" s="60">
         <f t="shared" si="0"/>
         <v>200809.2</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="14" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
+      <c r="A11" s="70">
         <v>45702</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="63">
         <v>10000</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="60">
         <v>13.788</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="60">
         <f>C11*D11</f>
         <v>137880</v>
       </c>
-      <c r="F11" s="13"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="21">
+      <c r="F11" s="59"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="60">
         <f t="shared" si="0"/>
         <v>62929.200000000012</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21">
+      <c r="A12" s="61"/>
+      <c r="B12" s="58"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60">
         <f t="shared" ref="E12:E14" si="1">C12*D12</f>
         <v>0</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="64">
         <v>45713</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="62">
         <v>466272</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="I12" s="21">
+      <c r="I12" s="60">
         <f t="shared" si="0"/>
         <v>529201.19999999995</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="56">
+      <c r="A13" s="73">
         <v>45718</v>
       </c>
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="58">
+      <c r="C13" s="75">
         <v>1</v>
       </c>
-      <c r="D13" s="55">
+      <c r="D13" s="76">
         <v>44910</v>
       </c>
-      <c r="E13" s="55">
+      <c r="E13" s="76">
         <f t="shared" si="1"/>
         <v>44910</v>
       </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="21">
+      <c r="F13" s="64"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="60">
         <f t="shared" si="0"/>
         <v>484291.19999999995</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="59"/>
-      <c r="B14" s="57" t="s">
+      <c r="A14" s="77"/>
+      <c r="B14" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="58">
+      <c r="C14" s="75">
         <v>1</v>
       </c>
-      <c r="D14" s="55">
+      <c r="D14" s="76">
         <v>15261.6</v>
       </c>
-      <c r="E14" s="55">
+      <c r="E14" s="76">
         <f t="shared" si="1"/>
         <v>15261.6</v>
       </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="21">
+      <c r="F14" s="64"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="60">
         <f t="shared" si="0"/>
         <v>469029.6</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="5">
+      <c r="A15" s="64">
         <v>45720</v>
       </c>
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="63">
         <v>5986</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="60">
         <v>13.788</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="60">
         <f>C15*D15</f>
         <v>82534.968000000008</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="21">
+      <c r="F15" s="61"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="60">
         <f t="shared" si="0"/>
         <v>386494.63199999998</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="28" t="s">
+      <c r="A16" s="61"/>
+      <c r="B16" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="63">
         <v>9823</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="60">
         <v>25.776</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="60">
         <f t="shared" ref="E16:E17" si="2">C16*D16</f>
         <v>253197.64799999999</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="21">
+      <c r="F16" s="61"/>
+      <c r="G16" s="62"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="60">
         <f t="shared" si="0"/>
         <v>133296.984</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-      <c r="B17" s="28" t="s">
+      <c r="A17" s="61"/>
+      <c r="B17" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="63">
         <v>2932</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="60">
         <v>24.744</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="60">
         <f t="shared" si="2"/>
         <v>72549.407999999996</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="21">
+      <c r="F17" s="61"/>
+      <c r="G17" s="62"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="60">
         <f t="shared" si="0"/>
         <v>60747.576000000001</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="5">
+      <c r="A18" s="64">
         <v>45742</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="51">
-        <v>0</v>
-      </c>
-      <c r="D18" s="52">
-        <v>0</v>
-      </c>
-      <c r="E18" s="52">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="21">
+      <c r="C18" s="78">
+        <v>0</v>
+      </c>
+      <c r="D18" s="79">
+        <v>0</v>
+      </c>
+      <c r="E18" s="79">
+        <v>0</v>
+      </c>
+      <c r="F18" s="61"/>
+      <c r="G18" s="62"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="60">
         <f t="shared" si="0"/>
         <v>60747.576000000001</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="34"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="23"/>
-      <c r="I19" s="36">
+      <c r="B19" s="66"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="68">
         <f t="shared" si="0"/>
         <v>60747.576000000001</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="3"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="5">
+      <c r="A20" s="61"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="63"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="64">
         <v>45763</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="62">
         <v>149976</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="H20" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="I20" s="21">
+      <c r="I20" s="60">
         <f t="shared" si="0"/>
         <v>210723.576</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="5">
+      <c r="A21" s="64">
         <v>45771</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="63">
         <v>6005</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="60">
         <v>25</v>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="60">
         <f t="shared" ref="E21:E23" si="3">C21*D21</f>
         <v>150125</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="21">
+      <c r="F21" s="61"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="60">
         <f t="shared" si="0"/>
         <v>60598.576000000001</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
-      <c r="B22" s="28" t="s">
+      <c r="A22" s="61"/>
+      <c r="B22" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="20">
+      <c r="C22" s="63">
         <v>2000</v>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="60">
         <v>25.776</v>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="60">
         <f t="shared" si="3"/>
         <v>51552</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="21">
+      <c r="F22" s="61"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="60">
         <f t="shared" si="0"/>
         <v>9046.5760000000009</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="20">
+      <c r="C23" s="63">
         <v>1805</v>
       </c>
-      <c r="D23" s="21">
+      <c r="D23" s="60">
         <v>24.995999999999999</v>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="60">
         <f t="shared" si="3"/>
         <v>45117.78</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="21">
+      <c r="F23" s="61"/>
+      <c r="G23" s="62"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="60">
         <f t="shared" si="0"/>
         <v>-36071.203999999998</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="63" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="61" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="C24" s="20">
+      <c r="C24" s="63">
         <v>9.9</v>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="60">
         <v>682</v>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="60">
         <f>C24*D24</f>
         <v>6751.8</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="61" t="s">
         <v>73</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="62">
         <v>245268</v>
       </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="21">
+      <c r="H24" s="61"/>
+      <c r="I24" s="60">
         <f t="shared" si="0"/>
         <v>202444.99599999998</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="63" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="61" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="58" t="s">
         <v>75</v>
       </c>
-      <c r="C25" s="20">
+      <c r="C25" s="63">
         <v>20</v>
       </c>
-      <c r="D25" s="21">
+      <c r="D25" s="60">
         <v>692</v>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="60">
         <f>C25*D25</f>
         <v>13840</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="21">
+      <c r="F25" s="61"/>
+      <c r="G25" s="62"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="60">
         <f t="shared" si="0"/>
         <v>188604.99599999998</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="61" t="s">
         <v>74</v>
       </c>
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="58" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="20">
+      <c r="C26" s="63">
         <v>660</v>
       </c>
-      <c r="D26" s="21">
+      <c r="D26" s="60">
         <v>33</v>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="60">
         <f>C26*D26</f>
         <v>21780</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="21">
+      <c r="F26" s="61"/>
+      <c r="G26" s="62"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="60">
         <f t="shared" si="0"/>
         <v>166824.99599999998</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="3"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="21">
-        <f t="shared" si="0"/>
-        <v>166824.99599999998</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="3"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="21">
-        <f t="shared" si="0"/>
-        <v>166824.99599999998</v>
+    <row r="27" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A27" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="63">
+        <v>9.9</v>
+      </c>
+      <c r="D27" s="60">
+        <v>682</v>
+      </c>
+      <c r="E27" s="60">
+        <f>C27*D27</f>
+        <v>6751.8</v>
+      </c>
+      <c r="F27" s="61"/>
+      <c r="G27" s="62"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="60">
+        <f t="shared" si="0"/>
+        <v>160073.196</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A28" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" s="58" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" s="63">
+        <v>20</v>
+      </c>
+      <c r="D28" s="60">
+        <v>692</v>
+      </c>
+      <c r="E28" s="60">
+        <f>C28*D28</f>
+        <v>13840</v>
+      </c>
+      <c r="F28" s="61"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="60">
+        <f t="shared" si="0"/>
+        <v>146233.196</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="3"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="21">
-        <f t="shared" si="0"/>
-        <v>166824.99599999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E30" s="37">
-        <f>SUM(E3:E27)</f>
-        <v>1097870.6040000001</v>
-      </c>
-      <c r="G30" s="7">
-        <f>SUM(G2:G28)</f>
+      <c r="A29" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="63">
+        <v>660</v>
+      </c>
+      <c r="D29" s="60">
+        <v>33</v>
+      </c>
+      <c r="E29" s="60">
+        <f>C29*D29</f>
+        <v>21780</v>
+      </c>
+      <c r="F29" s="61"/>
+      <c r="G29" s="62"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="60">
+        <f t="shared" ref="I29:I34" si="4">I28-E29+G29</f>
+        <v>124453.196</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A30" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="59">
+        <v>9.9</v>
+      </c>
+      <c r="D30" s="60">
+        <v>682</v>
+      </c>
+      <c r="E30" s="60">
+        <f>C30*D30</f>
+        <v>6751.8</v>
+      </c>
+      <c r="F30" s="61"/>
+      <c r="G30" s="62"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="60">
+        <f t="shared" si="4"/>
+        <v>117701.39599999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A31" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="58" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="59">
+        <v>20</v>
+      </c>
+      <c r="D31" s="60">
+        <v>692</v>
+      </c>
+      <c r="E31" s="60">
+        <f>C31*D31</f>
+        <v>13840</v>
+      </c>
+      <c r="F31" s="61"/>
+      <c r="G31" s="62"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="60">
+        <f t="shared" si="4"/>
+        <v>103861.39599999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" s="59">
+        <v>660</v>
+      </c>
+      <c r="D32" s="60">
+        <v>33</v>
+      </c>
+      <c r="E32" s="60">
+        <f>C32*D32</f>
+        <v>21780</v>
+      </c>
+      <c r="F32" s="61"/>
+      <c r="G32" s="62"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="60">
+        <f t="shared" si="4"/>
+        <v>82081.395999999993</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="61"/>
+      <c r="B33" s="58"/>
+      <c r="C33" s="59"/>
+      <c r="D33" s="60"/>
+      <c r="E33" s="60"/>
+      <c r="F33" s="61"/>
+      <c r="G33" s="62"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="60">
+        <f t="shared" si="4"/>
+        <v>82081.395999999993</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="80"/>
+      <c r="B34" s="81"/>
+      <c r="C34" s="82"/>
+      <c r="D34" s="83"/>
+      <c r="E34" s="83"/>
+      <c r="F34" s="80"/>
+      <c r="G34" s="84"/>
+      <c r="H34" s="80"/>
+      <c r="I34" s="83">
+        <f t="shared" si="4"/>
+        <v>82081.395999999993</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E35" s="35">
+        <f>SUM(E2:E34)</f>
+        <v>1182614.2040000001</v>
+      </c>
+      <c r="G35" s="7">
+        <f>SUM(G2:G34)</f>
         <v>1264695.6000000001</v>
       </c>
-      <c r="I30" s="37">
-        <f>G30-E30</f>
-        <v>166824.99600000004</v>
+      <c r="I35" s="35">
+        <f>G35-E35</f>
+        <v>82081.39599999995</v>
       </c>
     </row>
   </sheetData>
@@ -6793,13 +7003,13 @@
       <c r="A19" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B19" s="61" t="s">
+      <c r="B19" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="62">
+      <c r="C19" s="52">
         <v>9.1999999999999993</v>
       </c>
-      <c r="D19" s="63">
+      <c r="D19" s="53">
         <v>850</v>
       </c>
       <c r="E19" s="6">
@@ -6826,7 +7036,7 @@
       <c r="F20" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G20" s="64">
+      <c r="G20" s="54">
         <v>6728.28</v>
       </c>
       <c r="H20" s="3"/>
@@ -6904,7 +7114,7 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="40" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="3"/>
@@ -6939,10 +7149,10 @@
       </c>
     </row>
     <row r="4" spans="1:10" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="44">
+      <c r="A4" s="41">
         <v>45726</v>
       </c>
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="36" t="s">
         <v>34</v>
       </c>
       <c r="C4" s="13">
@@ -6964,7 +7174,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="42" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="23"/>
@@ -7006,13 +7216,13 @@
       </c>
     </row>
     <row r="7" spans="1:10" s="14" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="49">
+      <c r="A7" s="46">
         <v>45772</v>
       </c>
       <c r="B7" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="53">
+      <c r="C7" s="48">
         <v>180.9</v>
       </c>
       <c r="D7" s="21">
@@ -7029,7 +7239,7 @@
         <f t="shared" si="0"/>
         <v>37828.5</v>
       </c>
-      <c r="J7" s="54" t="s">
+      <c r="J7" s="49" t="s">
         <v>36</v>
       </c>
     </row>

--- a/files_result_11.07.2025/Поставщики комплектующих.xlsx
+++ b/files_result_11.07.2025/Поставщики комплектующих.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07CC4A65-2E59-4D92-BDB2-B11F65CD02A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ADE5935-C2AD-4F5E-8FBF-FA9A4D190A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,6 +35,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
